--- a/Data/EXCEL/Transfer/dividend/test/0050-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/test/0050-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\dividend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3CAF9E9-1011-4EDD-8B31-0859F9599D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD887F0F-DAB8-45FF-91C3-E84D04CD089A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{532CF67D-D6F4-4DB3-8DBC-00B5ED60AF15}"/>
+    <workbookView xWindow="8895" yWindow="1080" windowWidth="22845" windowHeight="19530" xr2:uid="{532CF67D-D6F4-4DB3-8DBC-00B5ED60AF15}"/>
   </bookViews>
   <sheets>
     <sheet name="0050-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="65">
   <si>
     <t>股利</t>
   </si>
@@ -34,184 +34,193 @@
     <t>發放</t>
   </si>
   <si>
+    <t>現金+股票殖利率</t>
+  </si>
+  <si>
+    <t>股東股利 (元/股)</t>
+  </si>
+  <si>
+    <t>花費</t>
+  </si>
+  <si>
+    <t>日數</t>
+  </si>
+  <si>
+    <t>填權</t>
+  </si>
+  <si>
+    <t>現金股利</t>
+  </si>
+  <si>
+    <t>股票股利</t>
+  </si>
+  <si>
+    <t>合計</t>
+  </si>
+  <si>
+    <t>股價</t>
+  </si>
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>除權/息前</t>
+  </si>
+  <si>
+    <t>年均價</t>
+  </si>
+  <si>
+    <t>盈餘</t>
+  </si>
+  <si>
+    <t>公積</t>
+  </si>
+  <si>
+    <t>除息</t>
+  </si>
+  <si>
+    <t>除權</t>
+  </si>
+  <si>
+    <t>利率</t>
+  </si>
+  <si>
+    <t>價格</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>    ∟</t>
+  </si>
+  <si>
+    <t>H2 </t>
+  </si>
+  <si>
+    <t>'26/01/22</t>
+  </si>
+  <si>
+    <t>H1 </t>
+  </si>
+  <si>
+    <t>'25/07/21</t>
+  </si>
+  <si>
+    <t>'25/01/17</t>
+  </si>
+  <si>
+    <t>'24/07/16</t>
+  </si>
+  <si>
+    <t>'24/01/17</t>
+  </si>
+  <si>
+    <t>'23/07/18</t>
+  </si>
+  <si>
+    <t>'23/01/30</t>
+  </si>
+  <si>
+    <t>'22/07/18</t>
+  </si>
+  <si>
+    <t>'22/01/21</t>
+  </si>
+  <si>
+    <t>'21/07/21</t>
+  </si>
+  <si>
+    <t>'21/01/22</t>
+  </si>
+  <si>
+    <t>'20/07/21</t>
+  </si>
+  <si>
+    <t>'20/01/31</t>
+  </si>
+  <si>
+    <t>'19/07/19</t>
+  </si>
+  <si>
+    <t>'19/01/22</t>
+  </si>
+  <si>
+    <t>'18/07/23</t>
+  </si>
+  <si>
+    <t>'18/01/29</t>
+  </si>
+  <si>
+    <t>'17/07/31</t>
+  </si>
+  <si>
+    <t>'17/02/08</t>
+  </si>
+  <si>
+    <t>'16/07/28</t>
+  </si>
+  <si>
+    <t> '15/10/26 </t>
+  </si>
+  <si>
+    <t> '14/10/24 </t>
+  </si>
+  <si>
+    <t> '13/10/24 </t>
+  </si>
+  <si>
+    <t> '12/10/24 </t>
+  </si>
+  <si>
+    <t> '11/10/26 </t>
+  </si>
+  <si>
+    <t> '10/10/25 </t>
+  </si>
+  <si>
+    <t> '09/10/23 </t>
+  </si>
+  <si>
+    <t> '08/10/24 </t>
+  </si>
+  <si>
+    <t> '07/10/24 </t>
+  </si>
+  <si>
+    <t> '06/10/26 </t>
+  </si>
+  <si>
+    <t> '05/05/19 </t>
+  </si>
+  <si>
+    <t> 無 </t>
+  </si>
+  <si>
+    <t>累計</t>
+  </si>
+  <si>
     <t>股利政策</t>
-  </si>
-  <si>
-    <t>現金+股票殖利率</t>
-  </si>
-  <si>
-    <t>股東股利 (元/股)</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
   <si>
     <t>填息</t>
-  </si>
-  <si>
-    <t>花費</t>
-  </si>
-  <si>
-    <t>日數</t>
-  </si>
-  <si>
-    <t>填權</t>
-  </si>
-  <si>
-    <t>現金股利</t>
-  </si>
-  <si>
-    <t>股票股利</t>
-  </si>
-  <si>
-    <t>合計</t>
-  </si>
-  <si>
-    <t>股價</t>
-  </si>
-  <si>
-    <t>年度</t>
-  </si>
-  <si>
-    <t>除權/息前</t>
-  </si>
-  <si>
-    <t>年均價</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>價格</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
   <si>
     <t>成交價</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
   <si>
     <t>最高價</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
   <si>
     <t>最低價</t>
-  </si>
-  <si>
-    <t>盈餘</t>
-  </si>
-  <si>
-    <t>公積</t>
-  </si>
-  <si>
-    <t>除息</t>
-  </si>
-  <si>
-    <t>除權</t>
-  </si>
-  <si>
-    <t>利率</t>
-  </si>
-  <si>
-    <t>價格</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>    ∟</t>
-  </si>
-  <si>
-    <t>H2 </t>
-  </si>
-  <si>
-    <t>'26/01/22</t>
-  </si>
-  <si>
-    <t>H1 </t>
-  </si>
-  <si>
-    <t>'25/07/21</t>
-  </si>
-  <si>
-    <t>'25/01/17</t>
-  </si>
-  <si>
-    <t>'24/07/16</t>
-  </si>
-  <si>
-    <t>'24/01/17</t>
-  </si>
-  <si>
-    <t>'23/07/18</t>
-  </si>
-  <si>
-    <t>'23/01/30</t>
-  </si>
-  <si>
-    <t>'22/07/18</t>
-  </si>
-  <si>
-    <t>'22/01/21</t>
-  </si>
-  <si>
-    <t>'21/07/21</t>
-  </si>
-  <si>
-    <t>'21/01/22</t>
-  </si>
-  <si>
-    <t>'20/07/21</t>
-  </si>
-  <si>
-    <t>'20/01/31</t>
-  </si>
-  <si>
-    <t>'19/07/19</t>
-  </si>
-  <si>
-    <t>'19/01/22</t>
-  </si>
-  <si>
-    <t>'18/07/23</t>
-  </si>
-  <si>
-    <t>'18/01/29</t>
-  </si>
-  <si>
-    <t>'17/07/31</t>
-  </si>
-  <si>
-    <t>'17/02/08</t>
-  </si>
-  <si>
-    <t>'16/07/28</t>
-  </si>
-  <si>
-    <t> '15/10/26 </t>
-  </si>
-  <si>
-    <t> '14/10/24 </t>
-  </si>
-  <si>
-    <t> '13/10/24 </t>
-  </si>
-  <si>
-    <t> '12/10/24 </t>
-  </si>
-  <si>
-    <t> '11/10/26 </t>
-  </si>
-  <si>
-    <t> '10/10/25 </t>
-  </si>
-  <si>
-    <t> '09/10/23 </t>
-  </si>
-  <si>
-    <t> '08/10/24 </t>
-  </si>
-  <si>
-    <t> '07/10/24 </t>
-  </si>
-  <si>
-    <t> '06/10/26 </t>
-  </si>
-  <si>
-    <t> '05/05/19 </t>
-  </si>
-  <si>
-    <t> 無 </t>
-  </si>
-  <si>
-    <t>累計</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1092,6 +1101,24 @@
     <xf numFmtId="0" fontId="22" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1131,25 +1158,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1549,202 +1558,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26"/>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="20"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="26"/>
     </row>
     <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="28"/>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="34"/>
+      <c r="D2" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="24"/>
       <c r="K2" s="5" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="29"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="31"/>
+        <v>8</v>
+      </c>
+      <c r="M2" s="35"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="37"/>
     </row>
     <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="32" t="s">
+      <c r="D3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="38"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="38"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="R3" s="34"/>
-      <c r="S3" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="T3" s="34"/>
-      <c r="U3" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="34"/>
-      <c r="W3" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="X3" s="34"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="24"/>
+      <c r="S3" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="24"/>
+      <c r="U3" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="V3" s="24"/>
+      <c r="W3" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="X3" s="24"/>
     </row>
     <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="7"/>
       <c r="D4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="T4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="V4" s="8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="35">
+      <c r="A5" s="19">
         <v>2025</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="20"/>
       <c r="C5" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D5" s="10">
         <v>1.36</v>
@@ -1768,43 +1777,43 @@
         <v>1.36</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M5" s="11">
         <v>2026</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P5" s="10">
         <v>2.09</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R5" s="10">
         <v>1.72</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T5" s="10">
         <v>1.84</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V5" s="10">
         <v>1.47</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X5" s="10">
         <v>2.2999999999999998</v>
@@ -1812,13 +1821,13 @@
     </row>
     <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D6" s="10">
         <v>1</v>
@@ -1845,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M6" s="13">
         <v>2026</v>
@@ -1854,7 +1863,7 @@
         <v>71.849999999999994</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P6" s="10">
         <v>1.39</v>
@@ -1886,13 +1895,13 @@
     </row>
     <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D7" s="10">
         <v>0.36</v>
@@ -1919,7 +1928,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M7" s="13">
         <v>2025</v>
@@ -1928,7 +1937,7 @@
         <v>51.45</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P7" s="10">
         <v>0.7</v>
@@ -1959,12 +1968,12 @@
       </c>
     </row>
     <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="37">
+      <c r="A8" s="21">
         <v>2024</v>
       </c>
-      <c r="B8" s="38"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D8" s="15">
         <v>3.7</v>
@@ -1988,43 +1997,43 @@
         <v>3.7</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M8" s="16">
         <v>2025</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P8" s="15">
         <v>1.87</v>
       </c>
       <c r="Q8" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R8" s="15">
         <v>3.02</v>
       </c>
       <c r="S8" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T8" s="15">
         <v>4.63</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V8" s="15">
         <v>1.8</v>
       </c>
       <c r="W8" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X8" s="15">
         <v>6.62</v>
@@ -2032,13 +2041,13 @@
     </row>
     <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>33</v>
       </c>
       <c r="D9" s="15">
         <v>2.7</v>
@@ -2065,7 +2074,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M9" s="18">
         <v>2025</v>
@@ -2074,7 +2083,7 @@
         <v>198</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P9" s="15">
         <v>1.36</v>
@@ -2106,13 +2115,13 @@
     </row>
     <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
@@ -2139,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M10" s="18">
         <v>2024</v>
@@ -2148,7 +2157,7 @@
         <v>196.7</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P10" s="15">
         <v>0.51</v>
@@ -2179,12 +2188,12 @@
       </c>
     </row>
     <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="19">
         <v>2023</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D11" s="10">
         <v>4.9000000000000004</v>
@@ -2208,43 +2217,43 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M11" s="11">
         <v>2024</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P11" s="10">
         <v>3.72</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R11" s="10">
         <v>3.27</v>
       </c>
       <c r="S11" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T11" s="10">
         <v>2.94</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V11" s="10">
         <v>2.88</v>
       </c>
       <c r="W11" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X11" s="10">
         <v>4.1100000000000003</v>
@@ -2252,13 +2261,13 @@
     </row>
     <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D12" s="10">
         <v>3</v>
@@ -2285,7 +2294,7 @@
         <v>3</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M12" s="13">
         <v>2024</v>
@@ -2294,7 +2303,7 @@
         <v>131.6</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P12" s="10">
         <v>2.2799999999999998</v>
@@ -2326,13 +2335,13 @@
     </row>
     <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>36</v>
       </c>
       <c r="D13" s="10">
         <v>1.9</v>
@@ -2359,7 +2368,7 @@
         <v>87</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M13" s="13">
         <v>2023</v>
@@ -2368,7 +2377,7 @@
         <v>132</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P13" s="10">
         <v>1.44</v>
@@ -2399,12 +2408,12 @@
       </c>
     </row>
     <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="37">
+      <c r="A14" s="21">
         <v>2022</v>
       </c>
-      <c r="B14" s="38"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D14" s="15">
         <v>4.4000000000000004</v>
@@ -2428,43 +2437,43 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M14" s="16">
         <v>2023</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O14" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P14" s="15">
         <v>3.76</v>
       </c>
       <c r="Q14" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R14" s="15">
         <v>3.56</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T14" s="15">
         <v>3.55</v>
       </c>
       <c r="U14" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V14" s="15">
         <v>3.09</v>
       </c>
       <c r="W14" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X14" s="15">
         <v>4.26</v>
@@ -2472,13 +2481,13 @@
     </row>
     <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15" s="15">
         <v>2.6</v>
@@ -2505,7 +2514,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M15" s="18">
         <v>2023</v>
@@ -2514,7 +2523,7 @@
         <v>118.1</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P15" s="15">
         <v>2.2000000000000002</v>
@@ -2546,13 +2555,13 @@
     </row>
     <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D16" s="15">
         <v>1.8</v>
@@ -2579,7 +2588,7 @@
         <v>3</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M16" s="18">
         <v>2022</v>
@@ -2588,7 +2597,7 @@
         <v>115.5</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P16" s="15">
         <v>1.56</v>
@@ -2619,12 +2628,12 @@
       </c>
     </row>
     <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="35">
+      <c r="A17" s="19">
         <v>2021</v>
       </c>
-      <c r="B17" s="36"/>
+      <c r="B17" s="20"/>
       <c r="C17" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D17" s="10">
         <v>3.55</v>
@@ -2648,43 +2657,43 @@
         <v>3.55</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M17" s="11">
         <v>2022</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P17" s="10">
         <v>2.4</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R17" s="10">
         <v>2.88</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T17" s="10">
         <v>3.14</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V17" s="10">
         <v>2.34</v>
       </c>
       <c r="W17" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X17" s="10">
         <v>3.6</v>
@@ -2692,13 +2701,13 @@
     </row>
     <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D18" s="10">
         <v>3.2</v>
@@ -2725,7 +2734,7 @@
         <v>511</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M18" s="13">
         <v>2022</v>
@@ -2734,7 +2743,7 @@
         <v>149.1</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P18" s="10">
         <v>2.15</v>
@@ -2766,13 +2775,13 @@
     </row>
     <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D19" s="10">
         <v>0.35</v>
@@ -2799,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M19" s="13">
         <v>2021</v>
@@ -2808,7 +2817,7 @@
         <v>137.19999999999999</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P19" s="10">
         <v>0.26</v>
@@ -2839,12 +2848,12 @@
       </c>
     </row>
     <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="37">
+      <c r="A20" s="21">
         <v>2020</v>
       </c>
-      <c r="B20" s="38"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D20" s="15">
         <v>3.75</v>
@@ -2868,43 +2877,43 @@
         <v>3.75</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M20" s="16">
         <v>2021</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P20" s="15">
         <v>2.85</v>
       </c>
       <c r="Q20" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R20" s="15">
         <v>2.95</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T20" s="15">
         <v>2.67</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V20" s="15">
         <v>2.66</v>
       </c>
       <c r="W20" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X20" s="15">
         <v>3.56</v>
@@ -2912,13 +2921,13 @@
     </row>
     <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D21" s="15">
         <v>3.05</v>
@@ -2945,7 +2954,7 @@
         <v>150</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M21" s="18">
         <v>2021</v>
@@ -2954,7 +2963,7 @@
         <v>143</v>
       </c>
       <c r="O21" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P21" s="15">
         <v>2.13</v>
@@ -2986,13 +2995,13 @@
     </row>
     <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D22" s="15">
         <v>0.7</v>
@@ -3019,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M22" s="18">
         <v>2020</v>
@@ -3028,7 +3037,7 @@
         <v>97.05</v>
       </c>
       <c r="O22" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P22" s="15">
         <v>0.72</v>
@@ -3059,12 +3068,12 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="35">
+      <c r="A23" s="19">
         <v>2019</v>
       </c>
-      <c r="B23" s="36"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D23" s="10">
         <v>3.6</v>
@@ -3088,43 +3097,43 @@
         <v>3.6</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M23" s="11">
         <v>2020</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P23" s="10">
         <v>3.99</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R23" s="10">
         <v>3.83</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T23" s="10">
         <v>3.09</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V23" s="10">
         <v>3.08</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X23" s="10">
         <v>5.28</v>
@@ -3132,13 +3141,13 @@
     </row>
     <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D24" s="10">
         <v>2.9</v>
@@ -3165,7 +3174,7 @@
         <v>5</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M24" s="13">
         <v>2020</v>
@@ -3174,7 +3183,7 @@
         <v>92.15</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P24" s="10">
         <v>3.15</v>
@@ -3206,13 +3215,13 @@
     </row>
     <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D25" s="10">
         <v>0.7</v>
@@ -3239,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M25" s="13">
         <v>2019</v>
@@ -3248,7 +3257,7 @@
         <v>82.7</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P25" s="10">
         <v>0.85</v>
@@ -3279,12 +3288,12 @@
       </c>
     </row>
     <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="37">
+      <c r="A26" s="21">
         <v>2018</v>
       </c>
-      <c r="B26" s="38"/>
+      <c r="B26" s="22"/>
       <c r="C26" s="16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D26" s="15">
         <v>3</v>
@@ -3308,43 +3317,43 @@
         <v>3</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M26" s="16">
         <v>2019</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O26" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P26" s="15">
         <v>3.83</v>
       </c>
       <c r="Q26" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R26" s="15">
         <v>3.63</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T26" s="15">
         <v>3.3</v>
       </c>
       <c r="U26" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V26" s="15">
         <v>3.13</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X26" s="15">
         <v>4.1500000000000004</v>
@@ -3352,13 +3361,13 @@
     </row>
     <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D27" s="15">
         <v>2.2999999999999998</v>
@@ -3385,7 +3394,7 @@
         <v>15</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M27" s="18">
         <v>2019</v>
@@ -3394,7 +3403,7 @@
         <v>76.5</v>
       </c>
       <c r="O27" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P27" s="15">
         <v>3.01</v>
@@ -3426,13 +3435,13 @@
     </row>
     <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D28" s="15">
         <v>0.7</v>
@@ -3459,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M28" s="18">
         <v>2018</v>
@@ -3468,7 +3477,7 @@
         <v>84.65</v>
       </c>
       <c r="O28" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P28" s="15">
         <v>0.83</v>
@@ -3499,12 +3508,12 @@
       </c>
     </row>
     <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="35">
+      <c r="A29" s="19">
         <v>2017</v>
       </c>
-      <c r="B29" s="36"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D29" s="10">
         <v>2.9</v>
@@ -3528,43 +3537,43 @@
         <v>2.9</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M29" s="11">
         <v>2018</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P29" s="10">
         <v>3.37</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R29" s="10">
         <v>3.58</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T29" s="10">
         <v>3.77</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V29" s="10">
         <v>3.31</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X29" s="10">
         <v>3.98</v>
@@ -3572,13 +3581,13 @@
     </row>
     <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D30" s="10">
         <v>2.2000000000000002</v>
@@ -3605,7 +3614,7 @@
         <v>143</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M30" s="13">
         <v>2018</v>
@@ -3614,7 +3623,7 @@
         <v>87.5</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P30" s="10">
         <v>2.5099999999999998</v>
@@ -3646,13 +3655,13 @@
     </row>
     <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D31" s="10">
         <v>0.7</v>
@@ -3679,7 +3688,7 @@
         <v>2</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13">
         <v>2017</v>
@@ -3688,7 +3697,7 @@
         <v>82.1</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P31" s="10">
         <v>0.85</v>
@@ -3719,12 +3728,12 @@
       </c>
     </row>
     <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="37">
+      <c r="A32" s="21">
         <v>2016</v>
       </c>
-      <c r="B32" s="38"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D32" s="15">
         <v>2.5499999999999998</v>
@@ -3748,43 +3757,43 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M32" s="16">
         <v>2017</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O32" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P32" s="15">
         <v>3.54</v>
       </c>
       <c r="Q32" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R32" s="15">
         <v>3.44</v>
       </c>
       <c r="S32" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T32" s="15">
         <v>3.25</v>
       </c>
       <c r="U32" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V32" s="15">
         <v>3.14</v>
       </c>
       <c r="W32" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="X32" s="15">
         <v>3.91</v>
@@ -3792,13 +3801,13 @@
     </row>
     <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D33" s="15">
         <v>1.7</v>
@@ -3825,7 +3834,7 @@
         <v>5</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M33" s="18">
         <v>2017</v>
@@ -3834,7 +3843,7 @@
         <v>73.3</v>
       </c>
       <c r="O33" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P33" s="15">
         <v>2.3199999999999998</v>
@@ -3866,13 +3875,13 @@
     </row>
     <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D34" s="15">
         <v>0.85</v>
@@ -3899,7 +3908,7 @@
         <v>7</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M34" s="18">
         <v>2016</v>
@@ -3908,7 +3917,7 @@
         <v>69.7</v>
       </c>
       <c r="O34" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P34" s="15">
         <v>1.22</v>
@@ -3939,12 +3948,12 @@
       </c>
     </row>
     <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="35">
+      <c r="A35" s="19">
         <v>2014</v>
       </c>
-      <c r="B35" s="36"/>
+      <c r="B35" s="20"/>
       <c r="C35" s="11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D35" s="10">
         <v>2</v>
@@ -3971,7 +3980,7 @@
         <v>168</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M35" s="11">
         <v>2015</v>
@@ -3980,7 +3989,7 @@
         <v>65.900000000000006</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P35" s="10">
         <v>3.03</v>
@@ -4011,12 +4020,12 @@
       </c>
     </row>
     <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="37">
+      <c r="A36" s="21">
         <v>2013</v>
       </c>
-      <c r="B36" s="38"/>
+      <c r="B36" s="22"/>
       <c r="C36" s="16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D36" s="15">
         <v>1.55</v>
@@ -4043,7 +4052,7 @@
         <v>6</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M36" s="16">
         <v>2014</v>
@@ -4052,7 +4061,7 @@
         <v>65.05</v>
       </c>
       <c r="O36" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P36" s="15">
         <v>2.38</v>
@@ -4083,12 +4092,12 @@
       </c>
     </row>
     <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="35">
+      <c r="A37" s="19">
         <v>2012</v>
       </c>
-      <c r="B37" s="36"/>
+      <c r="B37" s="20"/>
       <c r="C37" s="11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D37" s="10">
         <v>1.35</v>
@@ -4115,7 +4124,7 @@
         <v>48</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M37" s="11">
         <v>2013</v>
@@ -4124,7 +4133,7 @@
         <v>58.7</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P37" s="10">
         <v>2.2999999999999998</v>
@@ -4155,12 +4164,12 @@
       </c>
     </row>
     <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A38" s="37">
+      <c r="A38" s="21">
         <v>2011</v>
       </c>
-      <c r="B38" s="38"/>
+      <c r="B38" s="22"/>
       <c r="C38" s="16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D38" s="15">
         <v>1.85</v>
@@ -4187,7 +4196,7 @@
         <v>27</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M38" s="16">
         <v>2012</v>
@@ -4196,7 +4205,7 @@
         <v>52.9</v>
       </c>
       <c r="O38" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P38" s="15">
         <v>3.5</v>
@@ -4227,12 +4236,12 @@
       </c>
     </row>
     <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="35">
+      <c r="A39" s="19">
         <v>2010</v>
       </c>
-      <c r="B39" s="36"/>
+      <c r="B39" s="20"/>
       <c r="C39" s="11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D39" s="10">
         <v>1.95</v>
@@ -4259,7 +4268,7 @@
         <v>67</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M39" s="11">
         <v>2011</v>
@@ -4268,7 +4277,7 @@
         <v>53.6</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P39" s="10">
         <v>3.64</v>
@@ -4299,12 +4308,12 @@
       </c>
     </row>
     <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="37">
+      <c r="A40" s="21">
         <v>2009</v>
       </c>
-      <c r="B40" s="38"/>
+      <c r="B40" s="22"/>
       <c r="C40" s="16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D40" s="15">
         <v>2.2000000000000002</v>
@@ -4331,7 +4340,7 @@
         <v>8</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M40" s="16">
         <v>2010</v>
@@ -4340,7 +4349,7 @@
         <v>57.1</v>
       </c>
       <c r="O40" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P40" s="15">
         <v>3.85</v>
@@ -4371,12 +4380,12 @@
       </c>
     </row>
     <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A41" s="35">
+      <c r="A41" s="19">
         <v>2008</v>
       </c>
-      <c r="B41" s="36"/>
+      <c r="B41" s="20"/>
       <c r="C41" s="11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D41" s="10">
         <v>1</v>
@@ -4403,7 +4412,7 @@
         <v>2</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M41" s="11">
         <v>2009</v>
@@ -4412,7 +4421,7 @@
         <v>53.7</v>
       </c>
       <c r="O41" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P41" s="10">
         <v>1.86</v>
@@ -4443,12 +4452,12 @@
       </c>
     </row>
     <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A42" s="37">
+      <c r="A42" s="21">
         <v>2007</v>
       </c>
-      <c r="B42" s="38"/>
+      <c r="B42" s="22"/>
       <c r="C42" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D42" s="15">
         <v>2</v>
@@ -4475,7 +4484,7 @@
         <v>6</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M42" s="16">
         <v>2008</v>
@@ -4484,7 +4493,7 @@
         <v>35.51</v>
       </c>
       <c r="O42" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P42" s="15">
         <v>5.63</v>
@@ -4515,12 +4524,12 @@
       </c>
     </row>
     <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A43" s="35">
+      <c r="A43" s="19">
         <v>2006</v>
       </c>
-      <c r="B43" s="36"/>
+      <c r="B43" s="20"/>
       <c r="C43" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D43" s="10">
         <v>2.5</v>
@@ -4547,7 +4556,7 @@
         <v>4</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M43" s="11">
         <v>2007</v>
@@ -4556,7 +4565,7 @@
         <v>70.599999999999994</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P43" s="10">
         <v>3.54</v>
@@ -4587,12 +4596,12 @@
       </c>
     </row>
     <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="37">
+      <c r="A44" s="21">
         <v>2005</v>
       </c>
-      <c r="B44" s="38"/>
+      <c r="B44" s="22"/>
       <c r="C44" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D44" s="15">
         <v>4</v>
@@ -4619,7 +4628,7 @@
         <v>30</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M44" s="16">
         <v>2006</v>
@@ -4628,7 +4637,7 @@
         <v>57.4</v>
       </c>
       <c r="O44" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P44" s="15">
         <v>6.97</v>
@@ -4659,12 +4668,12 @@
       </c>
     </row>
     <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="35">
+      <c r="A45" s="19">
         <v>2004</v>
       </c>
-      <c r="B45" s="36"/>
+      <c r="B45" s="20"/>
       <c r="C45" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D45" s="10">
         <v>1.85</v>
@@ -4691,7 +4700,7 @@
         <v>18</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M45" s="11">
         <v>2005</v>
@@ -4700,7 +4709,7 @@
         <v>46.69</v>
       </c>
       <c r="O45" s="12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P45" s="10">
         <v>3.96</v>
@@ -4731,12 +4740,12 @@
       </c>
     </row>
     <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="37">
+      <c r="A46" s="21">
         <v>2003</v>
       </c>
-      <c r="B46" s="38"/>
+      <c r="B46" s="22"/>
       <c r="C46" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D46" s="15">
         <v>0</v>
@@ -4760,19 +4769,19 @@
         <v>0</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M46" s="16">
         <v>2004</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O46" s="17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P46" s="15">
         <v>0</v>
@@ -4803,10 +4812,10 @@
       </c>
     </row>
     <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" s="36"/>
+      <c r="A47" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="20"/>
       <c r="C47" s="10"/>
       <c r="D47" s="10">
         <v>55.96</v>
@@ -4846,6 +4855,34 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="D1:L1"/>
+    <mergeCell ref="M1:X2"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
@@ -4855,34 +4892,6 @@
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D1:L1"/>
-    <mergeCell ref="M1:X2"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
